--- a/Fylker.xlsx
+++ b/Fylker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tronder.sharepoint.com/sites/seksjonregional/Delte dokumenter/Statistikk/PowerBI/GitHub/mal/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="58" documentId="8_{F8BD9F77-780C-4D90-9BD3-284D667D7D15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6F16765-A614-47E0-9E4A-735A44DC5918}"/>
+  <xr:revisionPtr revIDLastSave="66" documentId="8_{F8BD9F77-780C-4D90-9BD3-284D667D7D15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{300EC738-0658-4B95-85A7-DED88B029F73}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D2EFAD6C-8952-4A8F-8394-39280D8D9D09}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="58">
   <si>
     <t>01</t>
   </si>
@@ -242,10 +242,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -560,7 +559,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C8C6B70-44F5-4CC2-8413-49A9181BA0D0}">
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" style="1" bestFit="1" customWidth="1"/>
@@ -1190,9 +1189,85 @@
         <v>39</v>
       </c>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B34" s="2"/>
-      <c r="D34" s="2"/>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B32" t="s">
+        <v>39</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D32" t="s">
+        <v>39</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F32" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B33" t="s">
+        <v>38</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D33" t="s">
+        <v>38</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F33" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B34" t="s">
+        <v>31</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D34" t="s">
+        <v>31</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F34" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B35" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D35" t="s">
+        <v>32</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F35" t="s">
+        <v>32</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D31">
@@ -1213,17 +1288,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="4c1e125b-b772-4d2d-8af8-eec310c9bc7c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e0dd9af2-4fb6-4c9d-b1e7-5953e7056a03">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x01010084524CC458AB204A9AE668594E7CAFE2" ma:contentTypeVersion="14" ma:contentTypeDescription="Opprett et nytt dokument." ma:contentTypeScope="" ma:versionID="ca53d91e785442f301400f43f2317227">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e0dd9af2-4fb6-4c9d-b1e7-5953e7056a03" xmlns:ns3="4c1e125b-b772-4d2d-8af8-eec310c9bc7c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="90962d3e54d2b9018c88f57cdf59aac8" ns2:_="" ns3:_="">
     <xsd:import namespace="e0dd9af2-4fb6-4c9d-b1e7-5953e7056a03"/>
@@ -1436,6 +1500,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="4c1e125b-b772-4d2d-8af8-eec310c9bc7c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e0dd9af2-4fb6-4c9d-b1e7-5953e7056a03">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EE60EF02-366D-46B3-97B1-8BA4084C1CD4}">
   <ds:schemaRefs>
@@ -1445,18 +1520,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFB53AFF-2738-4852-81F8-BF2B359A58E8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4c1e125b-b772-4d2d-8af8-eec310c9bc7c"/>
-    <ds:schemaRef ds:uri="e0dd9af2-4fb6-4c9d-b1e7-5953e7056a03"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C76E0FFE-0473-442C-B79D-E250FF05747A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1473,4 +1536,22 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFB53AFF-2738-4852-81F8-BF2B359A58E8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4c1e125b-b772-4d2d-8af8-eec310c9bc7c"/>
+    <ds:schemaRef ds:uri="e0dd9af2-4fb6-4c9d-b1e7-5953e7056a03"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{aa934675-04c4-4b3a-8711-305fdcbd5aa4}" enabled="1" method="Standard" siteId="{b6334d01-13b9-4531-a3a6-532e479d9a1a}" removed="0"/>
+</clbl:labelList>
 </file>